--- a/ExamenSeptimo.xlsx
+++ b/ExamenSeptimo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC\Escritorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98CB3283-C1E6-4204-A5E6-EACA21B76EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D0A870-A30C-43D9-85CF-A53D9295B0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="83">
   <si>
     <t>Nombre</t>
   </si>
@@ -282,6 +282,9 @@
   </si>
   <si>
     <t>25. Cuantos empleados tienen ventas mayores a 40000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ordenar la tabla desde el que tenga mayor salario al menor. </t>
   </si>
 </sst>
 </file>
@@ -319,7 +322,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -329,6 +332,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -359,7 +368,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -373,6 +382,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -381,10 +391,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -702,15 +717,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
@@ -1757,303 +1772,334 @@
       </c>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="8"/>
-      <c r="I41" s="8"/>
-      <c r="J41" s="8"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
       <c r="E43" s="1"/>
+      <c r="H43" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
       <c r="E44" s="1"/>
-      <c r="H44" s="5"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
+      <c r="H44" s="10"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="11"/>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
       <c r="E45" s="1"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="6"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="11"/>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
       <c r="E46" s="1"/>
-      <c r="H46" s="5"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="11"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
       <c r="E47" s="1"/>
-      <c r="H47" s="5"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
+      <c r="H47" s="10"/>
+      <c r="I47" s="11"/>
+      <c r="J47" s="11"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
       <c r="E48" s="1"/>
-      <c r="H48" s="5"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="11"/>
+      <c r="J48" s="11"/>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B49" s="5" t="s">
+      <c r="B49" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
       <c r="E49" s="1"/>
-      <c r="H49" s="5"/>
-      <c r="I49" s="6"/>
-      <c r="J49" s="6"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="11"/>
+      <c r="J49" s="11"/>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
       <c r="E50" s="1"/>
-      <c r="H50" s="5"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="6"/>
+      <c r="H50" s="10"/>
+      <c r="I50" s="11"/>
+      <c r="J50" s="11"/>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
       <c r="E51" s="1"/>
-      <c r="H51" s="5"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="6"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="11"/>
+      <c r="J51" s="11"/>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
       <c r="E52" s="1"/>
-      <c r="H52" s="5"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="6"/>
+      <c r="H52" s="10"/>
+      <c r="I52" s="11"/>
+      <c r="J52" s="11"/>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
       <c r="E53" s="1"/>
-      <c r="H53" s="5"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="6"/>
+      <c r="H53" s="10"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="11"/>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
       <c r="E54" s="1"/>
-      <c r="H54" s="5"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="11"/>
+      <c r="J54" s="11"/>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
       <c r="E55" s="1"/>
-      <c r="H55" s="5"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="6"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="11"/>
+      <c r="J55" s="11"/>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="7"/>
       <c r="E56" s="1"/>
-      <c r="H56" s="5"/>
-      <c r="I56" s="6"/>
-      <c r="J56" s="6"/>
+      <c r="H56" s="10"/>
+      <c r="I56" s="11"/>
+      <c r="J56" s="11"/>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
       <c r="E57" s="1"/>
-      <c r="H57" s="5"/>
-      <c r="I57" s="6"/>
-      <c r="J57" s="6"/>
+      <c r="H57" s="10"/>
+      <c r="I57" s="11"/>
+      <c r="J57" s="11"/>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7"/>
       <c r="E58" s="1"/>
-      <c r="H58" s="5"/>
-      <c r="I58" s="6"/>
-      <c r="J58" s="6"/>
+      <c r="H58" s="10"/>
+      <c r="I58" s="11"/>
+      <c r="J58" s="11"/>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B59" s="5" t="s">
+      <c r="B59" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6"/>
+      <c r="C59" s="7"/>
+      <c r="D59" s="7"/>
       <c r="E59" s="1"/>
-      <c r="H59" s="5"/>
-      <c r="I59" s="6"/>
-      <c r="J59" s="6"/>
+      <c r="H59" s="10"/>
+      <c r="I59" s="11"/>
+      <c r="J59" s="11"/>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B60" s="5" t="s">
+      <c r="B60" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C60" s="6"/>
-      <c r="D60" s="6"/>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
       <c r="E60" s="1"/>
-      <c r="H60" s="5"/>
-      <c r="I60" s="6"/>
-      <c r="J60" s="6"/>
+      <c r="H60" s="10"/>
+      <c r="I60" s="11"/>
+      <c r="J60" s="11"/>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B61" s="5" t="s">
+      <c r="B61" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
+      <c r="C61" s="7"/>
+      <c r="D61" s="7"/>
       <c r="E61" s="1"/>
-      <c r="H61" s="5"/>
-      <c r="I61" s="6"/>
-      <c r="J61" s="6"/>
+      <c r="H61" s="10"/>
+      <c r="I61" s="11"/>
+      <c r="J61" s="11"/>
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B62" s="5" t="s">
+      <c r="B62" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C62" s="6"/>
-      <c r="D62" s="6"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="7"/>
       <c r="E62" s="1"/>
-      <c r="H62" s="9"/>
-      <c r="I62" s="10"/>
-      <c r="J62" s="10"/>
+      <c r="H62" s="12"/>
+      <c r="I62" s="13"/>
+      <c r="J62" s="13"/>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B63" s="5" t="s">
+      <c r="B63" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
       <c r="E63" s="1"/>
-      <c r="H63" s="5"/>
-      <c r="I63" s="6"/>
-      <c r="J63" s="6"/>
+      <c r="H63" s="10"/>
+      <c r="I63" s="11"/>
+      <c r="J63" s="11"/>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B64" s="5" t="s">
+      <c r="B64" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="C64" s="6"/>
-      <c r="D64" s="6"/>
+      <c r="C64" s="7"/>
+      <c r="D64" s="7"/>
       <c r="E64" s="1"/>
-      <c r="H64" s="5"/>
-      <c r="I64" s="6"/>
-      <c r="J64" s="6"/>
+      <c r="H64" s="10"/>
+      <c r="I64" s="11"/>
+      <c r="J64" s="11"/>
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B65" s="5" t="s">
+      <c r="B65" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
+      <c r="C65" s="7"/>
+      <c r="D65" s="7"/>
       <c r="E65" s="1"/>
-      <c r="H65" s="5"/>
-      <c r="I65" s="6"/>
-      <c r="J65" s="6"/>
+      <c r="H65" s="10"/>
+      <c r="I65" s="11"/>
+      <c r="J65" s="11"/>
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B66" s="5" t="s">
+      <c r="B66" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C66" s="6"/>
-      <c r="D66" s="6"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="7"/>
       <c r="E66" s="1"/>
-      <c r="H66" s="5"/>
-      <c r="I66" s="6"/>
-      <c r="J66" s="6"/>
+      <c r="H66" s="10"/>
+      <c r="I66" s="11"/>
+      <c r="J66" s="11"/>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B67" s="5" t="s">
+      <c r="B67" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C67" s="6"/>
-      <c r="D67" s="6"/>
+      <c r="C67" s="7"/>
+      <c r="D67" s="7"/>
       <c r="E67" s="1"/>
-      <c r="H67" s="5"/>
-      <c r="I67" s="6"/>
-      <c r="J67" s="6"/>
+      <c r="H67" s="10"/>
+      <c r="I67" s="11"/>
+      <c r="J67" s="11"/>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="H68" s="5"/>
-      <c r="I68" s="6"/>
-      <c r="J68" s="6"/>
+      <c r="H68" s="6"/>
+      <c r="I68" s="7"/>
+      <c r="J68" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="53">
+  <mergeCells count="29">
+    <mergeCell ref="H68:J68"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B41:J41"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B54:D54"/>
     <mergeCell ref="B60:D60"/>
     <mergeCell ref="B61:D61"/>
     <mergeCell ref="B62:D62"/>
@@ -2062,51 +2108,6 @@
     <mergeCell ref="B57:D57"/>
     <mergeCell ref="B58:D58"/>
     <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B41:J41"/>
-    <mergeCell ref="B40:G40"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="H44:J44"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="H46:J46"/>
-    <mergeCell ref="H47:J47"/>
-    <mergeCell ref="H48:J48"/>
-    <mergeCell ref="H49:J49"/>
-    <mergeCell ref="H50:J50"/>
-    <mergeCell ref="H51:J51"/>
-    <mergeCell ref="H52:J52"/>
-    <mergeCell ref="H53:J53"/>
-    <mergeCell ref="H54:J54"/>
-    <mergeCell ref="H55:J55"/>
-    <mergeCell ref="H56:J56"/>
-    <mergeCell ref="H57:J57"/>
-    <mergeCell ref="H58:J58"/>
-    <mergeCell ref="H59:J59"/>
-    <mergeCell ref="H60:J60"/>
-    <mergeCell ref="H61:J61"/>
-    <mergeCell ref="H62:J62"/>
-    <mergeCell ref="H63:J63"/>
-    <mergeCell ref="H64:J64"/>
-    <mergeCell ref="H65:J65"/>
-    <mergeCell ref="H66:J66"/>
-    <mergeCell ref="H67:J67"/>
-    <mergeCell ref="H68:J68"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B67:D67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
